--- a/downloads/korrigierte_referenz/Projekte_2NF.xlsx
+++ b/downloads/korrigierte_referenz/Projekte_2NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R4fe32d56492849cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="2" r:id="R7fe6dbf3fd454e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="3" r:id="Rf8785232fbd54438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER" sheetId="1" r:id="R7e84ee902ca84943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJEKT" sheetId="2" r:id="Rf1e5a031d98340e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MITARBEITER_PROJEKT" sheetId="3" r:id="R3186e1a794c6414e"/>
   </x:sheets>
 </x:workbook>
 </file>
